--- a/全量数据/伦敦金现与汇率_北京时间1530收盘价.xlsx
+++ b/全量数据/伦敦金现与汇率_北京时间1530收盘价.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="北京时间1530" sheetId="1" r:id="Rd9a888f3e2604f25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="北京时间1530" sheetId="1" r:id="R1c1e207256ee4bcf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48352,6 +48352,17 @@
         <x:v>6.6679</x:v>
       </x:c>
     </x:row>
+    <x:row r="4531">
+      <x:c r="A4531" s="6" t="d">
+        <x:v>2026-10-28T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B4531" s="9" t="n">
+        <x:v>4038.01</x:v>
+      </x:c>
+      <x:c r="C4531" s="10" t="n">
+        <x:v>6.6649</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/全量数据/伦敦金现与汇率_北京时间1530收盘价.xlsx
+++ b/全量数据/伦敦金现与汇率_北京时间1530收盘价.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="北京时间1530" sheetId="1" r:id="R1c1e207256ee4bcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="北京时间1530" sheetId="1" r:id="R79158df477d944fd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48363,6 +48363,17 @@
         <x:v>6.6649</x:v>
       </x:c>
     </x:row>
+    <x:row r="4532">
+      <x:c r="A4532" s="6" t="d">
+        <x:v>2026-10-29T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B4532" s="9" t="n">
+        <x:v>4029.35</x:v>
+      </x:c>
+      <x:c r="C4532" s="10" t="n">
+        <x:v>6.6583</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/全量数据/伦敦金现与汇率_北京时间1530收盘价.xlsx
+++ b/全量数据/伦敦金现与汇率_北京时间1530收盘价.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="北京时间1530" sheetId="1" r:id="R79158df477d944fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="北京时间1530" sheetId="1" r:id="Rdf999916c3e94637"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -48374,6 +48374,17 @@
         <x:v>6.6583</x:v>
       </x:c>
     </x:row>
+    <x:row r="4533">
+      <x:c r="A4533" s="6" t="d">
+        <x:v>2026-10-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B4533" s="9" t="n">
+        <x:v>3984.78</x:v>
+      </x:c>
+      <x:c r="C4533" s="10" t="n">
+        <x:v>6.6522</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
